--- a/data.mn/public/datasets/apartment-prices-ulaanbaatar.xlsx
+++ b/data.mn/public/datasets/apartment-prices-ulaanbaatar.xlsx
@@ -414,13 +414,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1139,6 +1134,32 @@
       </c>
       <c r="C55" t="n">
         <v>4.78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4.86</v>
       </c>
     </row>
   </sheetData>
@@ -1152,13 +1173,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1877,6 +1893,32 @@
       </c>
       <c r="C55" t="n">
         <v>4.73</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="C56" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4.78</v>
       </c>
     </row>
   </sheetData>
